--- a/Data/National Accounts/PSA-15AFSA_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-15AFSA_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51ADF0DA-C3AD-44DC-A28B-7D7B7D4AC3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D600BA89-E64B-4257-A437-568D8D0E3759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AFSA" sheetId="1" r:id="rId1"/>
@@ -612,9 +612,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -622,6 +619,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23585,7 +23585,7 @@
     </row>
     <row r="3" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:149" x14ac:dyDescent="0.2">
@@ -23595,7 +23595,7 @@
     </row>
     <row r="6" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:149" x14ac:dyDescent="0.2">
@@ -23797,10 +23797,10 @@
         <v>141953.54745028628</v>
       </c>
       <c r="Z12" s="8">
-        <v>164662.76432675688</v>
+        <v>165551.08557171735</v>
       </c>
       <c r="AA12" s="8">
-        <v>176283.70305196708</v>
+        <v>176981.97468119673</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -24002,10 +24002,10 @@
         <v>368255.84238612547</v>
       </c>
       <c r="Z13" s="8">
-        <v>421294.13336453226</v>
+        <v>421831.49966219766</v>
       </c>
       <c r="AA13" s="8">
-        <v>458452.57549264899</v>
+        <v>459083.94801388832</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -24358,10 +24358,10 @@
         <v>510209.38983641175</v>
       </c>
       <c r="Z15" s="11">
-        <v>585956.8976912892</v>
+        <v>587382.58523391502</v>
       </c>
       <c r="AA15" s="11">
-        <v>634736.27854461607</v>
+        <v>636065.92269508506</v>
       </c>
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
@@ -24834,7 +24834,7 @@
     </row>
     <row r="22" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:149" x14ac:dyDescent="0.2">
@@ -24844,7 +24844,7 @@
     </row>
     <row r="25" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:149" x14ac:dyDescent="0.2">
@@ -25046,10 +25046,10 @@
         <v>121976.30995911067</v>
       </c>
       <c r="Z31" s="8">
-        <v>138146.58971226332</v>
+        <v>138897.18370087532</v>
       </c>
       <c r="AA31" s="8">
-        <v>145376.46576174349</v>
+        <v>145953.63464334054</v>
       </c>
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
@@ -25251,10 +25251,10 @@
         <v>282697.31699210487</v>
       </c>
       <c r="Z32" s="8">
-        <v>308517.0660537784</v>
+        <v>308915.11271332169</v>
       </c>
       <c r="AA32" s="8">
-        <v>327582.95981303847</v>
+        <v>328041.48429670895</v>
       </c>
       <c r="AB32" s="9"/>
       <c r="AC32" s="9"/>
@@ -25607,10 +25607,10 @@
         <v>404673.62695121556</v>
       </c>
       <c r="Z34" s="11">
-        <v>446663.65576604172</v>
+        <v>447812.29641419702</v>
       </c>
       <c r="AA34" s="11">
-        <v>472959.42557478196</v>
+        <v>473995.11894004949</v>
       </c>
       <c r="AB34" s="9"/>
       <c r="AC34" s="9"/>
@@ -26083,7 +26083,7 @@
     </row>
     <row r="41" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:149" x14ac:dyDescent="0.2">
@@ -26093,7 +26093,7 @@
     </row>
     <row r="44" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:149" x14ac:dyDescent="0.2">
@@ -26209,7 +26209,7 @@
         <v>46</v>
       </c>
       <c r="Z48" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA48" s="17"/>
     </row>
@@ -26290,10 +26290,10 @@
         <v>41.39010254491393</v>
       </c>
       <c r="Y50" s="18">
-        <v>15.997639568974932</v>
+        <v>16.623422623302318</v>
       </c>
       <c r="Z50" s="18">
-        <v>7.0574174876292091</v>
+        <v>6.9047503192164044</v>
       </c>
       <c r="AA50" s="18"/>
       <c r="AB50" s="9"/>
@@ -26488,10 +26488,10 @@
         <v>24.517862366295702</v>
       </c>
       <c r="Y51" s="18">
-        <v>14.402566062426473</v>
+        <v>14.548488064419288</v>
       </c>
       <c r="Z51" s="18">
-        <v>8.8200711059901522</v>
+        <v>8.8311205733859026</v>
       </c>
       <c r="AA51" s="18"/>
       <c r="AB51" s="9"/>
@@ -26832,10 +26832,10 @@
         <v>28.793954159676304</v>
       </c>
       <c r="Y53" s="18">
-        <v>14.846357076878647</v>
+        <v>15.125788928002137</v>
       </c>
       <c r="Z53" s="18">
-        <v>8.3247387385524405</v>
+        <v>8.2881819592562067</v>
       </c>
       <c r="AA53" s="18"/>
       <c r="AB53" s="9"/>
@@ -27294,7 +27294,7 @@
     </row>
     <row r="60" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:144" x14ac:dyDescent="0.2">
@@ -27304,7 +27304,7 @@
     </row>
     <row r="63" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:144" x14ac:dyDescent="0.2">
@@ -27420,7 +27420,7 @@
         <v>46</v>
       </c>
       <c r="Z67" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA67" s="6"/>
     </row>
@@ -27501,10 +27501,10 @@
         <v>35.559408655059229</v>
       </c>
       <c r="Y69" s="18">
-        <v>13.256901900519296</v>
+        <v>13.872262365894585</v>
       </c>
       <c r="Z69" s="18">
-        <v>5.2334813798435391</v>
+        <v>5.0803412671503594</v>
       </c>
       <c r="AA69" s="18"/>
       <c r="AB69" s="9"/>
@@ -27699,10 +27699,10 @@
         <v>18.212191723714795</v>
       </c>
       <c r="Y70" s="18">
-        <v>9.1333548320851747</v>
+        <v>9.2741579581206395</v>
       </c>
       <c r="Z70" s="18">
-        <v>6.1798506005293916</v>
+        <v>6.1914651618669296</v>
       </c>
       <c r="AA70" s="18"/>
       <c r="AB70" s="9"/>
@@ -28043,10 +28043,10 @@
         <v>22.954788252481634</v>
       </c>
       <c r="Y72" s="18">
-        <v>10.376270163977892</v>
+        <v>10.660113876949524</v>
       </c>
       <c r="Z72" s="18">
-        <v>5.8871523279954801</v>
+        <v>5.8468297399397784</v>
       </c>
       <c r="AA72" s="18"/>
       <c r="AB72" s="9"/>
@@ -28510,7 +28510,7 @@
     </row>
     <row r="78" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:149" x14ac:dyDescent="0.2">
@@ -28520,7 +28520,7 @@
     </row>
     <row r="81" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:149" x14ac:dyDescent="0.2">
@@ -28722,10 +28722,10 @@
         <v>116.37796511295713</v>
       </c>
       <c r="Z87" s="18">
-        <v>119.19423032426815</v>
+        <v>119.18966328953296</v>
       </c>
       <c r="AA87" s="18">
-        <v>121.26013803422437</v>
+        <v>121.25903895006012</v>
       </c>
       <c r="AB87" s="9"/>
       <c r="AC87" s="9"/>
@@ -28927,10 +28927,10 @@
         <v>130.26506452355545</v>
       </c>
       <c r="Z88" s="18">
-        <v>136.55456365940398</v>
+        <v>136.55256162674834</v>
       </c>
       <c r="AA88" s="18">
-        <v>139.95006814588336</v>
+        <v>139.94691829849583</v>
       </c>
       <c r="AB88" s="9"/>
       <c r="AC88" s="9"/>
@@ -29283,10 +29283,10 @@
         <v>126.07922924957964</v>
       </c>
       <c r="Z90" s="18">
-        <v>131.18526437669422</v>
+        <v>131.167140772442</v>
       </c>
       <c r="AA90" s="18">
-        <v>134.20522865639663</v>
+        <v>134.19250479149642</v>
       </c>
       <c r="AB90" s="9"/>
       <c r="AC90" s="9"/>
@@ -29457,7 +29457,7 @@
     </row>
     <row r="97" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:149" x14ac:dyDescent="0.2">
@@ -29467,7 +29467,7 @@
     </row>
     <row r="100" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" spans="1:149" x14ac:dyDescent="0.2">
@@ -29669,10 +29669,10 @@
         <v>27.822605831656837</v>
       </c>
       <c r="Z106" s="18">
-        <v>28.101514800071403</v>
+        <v>28.184541001635154</v>
       </c>
       <c r="AA106" s="18">
-        <v>27.772747361497469</v>
+        <v>27.824470446601445</v>
       </c>
       <c r="AB106" s="9"/>
       <c r="AC106" s="9"/>
@@ -29874,10 +29874,10 @@
         <v>72.177394168343156</v>
       </c>
       <c r="Z107" s="18">
-        <v>71.898485199928587</v>
+        <v>71.815458998364846</v>
       </c>
       <c r="AA107" s="18">
-        <v>72.227252638502534</v>
+        <v>72.175529553398547</v>
       </c>
       <c r="AB107" s="9"/>
       <c r="AC107" s="9"/>
@@ -30706,7 +30706,7 @@
     </row>
     <row r="116" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118" spans="1:149" x14ac:dyDescent="0.2">
@@ -30716,7 +30716,7 @@
     </row>
     <row r="119" spans="1:149" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120" spans="1:149" x14ac:dyDescent="0.2">
@@ -30918,10 +30918,10 @@
         <v>30.14189752815674</v>
       </c>
       <c r="Z125" s="18">
-        <v>30.92854946421323</v>
+        <v>31.016831117206422</v>
       </c>
       <c r="AA125" s="18">
-        <v>30.73761889512387</v>
+        <v>30.792223128736612</v>
       </c>
       <c r="AB125" s="9"/>
       <c r="AC125" s="9"/>
@@ -31123,10 +31123,10 @@
         <v>69.858102471843253</v>
       </c>
       <c r="Z126" s="18">
-        <v>69.071450535786767</v>
+        <v>68.983168882793578</v>
       </c>
       <c r="AA126" s="18">
-        <v>69.262381104876141</v>
+        <v>69.207776871263377</v>
       </c>
       <c r="AB126" s="9"/>
       <c r="AC126" s="9"/>
